--- a/product_upload/packages/10/file.xlsx
+++ b/product_upload/packages/10/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>XARELTO 15MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-7AA8605D6B90</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,6 +1048,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>XARELTO 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-0F022E8E0A13</t>
         </is>
       </c>
@@ -1061,7 +1076,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>XANAX 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-442C53FE9824</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1410,6 +1430,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>SYSTANE LUBRICANT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-A25136C1C823</t>
         </is>
       </c>
@@ -1433,7 +1458,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1608,6 +1633,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>ROACCUTANE 20MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-D08F0A2FA3C6</t>
         </is>
       </c>
@@ -1631,7 +1661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1802,6 +1832,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ROACCUTANE 10MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-9238E57F6519</t>
         </is>
       </c>
@@ -1825,7 +1860,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1996,6 +2031,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>RIZINO 5MG/5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-DF8B8BDB5351</t>
         </is>
       </c>
@@ -2019,7 +2059,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2182,6 +2222,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>RIVOTRIL TAB 2 MG</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-DE844224CC70</t>
         </is>
       </c>
@@ -2205,7 +2250,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2380,6 +2425,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>RIVOTRIL TAB 0.5MG</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-EB3A7830B663</t>
         </is>
       </c>
@@ -2403,7 +2453,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2578,6 +2628,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>RIVOTRIL 2.5MG-ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-FA85A749AC84</t>
         </is>
       </c>
@@ -2601,7 +2656,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2768,6 +2823,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>RITALIN TAB. 10MG</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-D163232F2366</t>
         </is>
       </c>
@@ -2791,7 +2851,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2952,6 +3012,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>RISPERDAL 4MG TAB</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-879911E61C6F</t>
         </is>
       </c>
@@ -2975,7 +3040,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3134,6 +3199,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>ROBITUSSIN-PE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-67FFF963991E</t>
         </is>
       </c>
@@ -3157,7 +3227,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3324,6 +3394,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ROLIP ointment</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-345829235D78</t>
         </is>
       </c>
@@ -3347,7 +3422,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3514,6 +3589,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ROFENAC-D 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-32CFD23050A3</t>
         </is>
       </c>
@@ -3537,7 +3617,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3700,6 +3780,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ROFENAC GEL 1%</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-FA151FA3523C</t>
         </is>
       </c>
@@ -3723,7 +3808,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3886,6 +3971,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ROFENAC GEL 1%</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-0022F8E822B2</t>
         </is>
       </c>
@@ -3909,7 +3999,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4070,6 +4160,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>RISPERDAL 3MG TAB</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-2850119ECEAE</t>
         </is>
       </c>
@@ -4093,7 +4188,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4260,6 +4355,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ROFENAC 25MG SUPPOSITORES</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-69CCAF417270</t>
         </is>
       </c>
@@ -4283,7 +4383,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4450,6 +4550,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ROFENAC 12.5 MG SUPP</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F0607CFFBC7A</t>
         </is>
       </c>
@@ -4473,7 +4578,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4632,6 +4737,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ROFENAC 100 MG SUPP</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-5E41987F63E7</t>
         </is>
       </c>
@@ -4655,7 +4765,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4822,6 +4932,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>ROFENAC 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-3574E86E345C</t>
         </is>
       </c>
@@ -4845,7 +4960,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5010,6 +5125,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>RISPERDAL 2MG TAB</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-2393B8D0B235</t>
         </is>
       </c>
@@ -5033,7 +5153,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5200,6 +5320,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>RINGERS INJECATION 500 ML SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-67BD76D9F176</t>
         </is>
       </c>
@@ -5223,7 +5348,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5382,6 +5507,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>RINGER SOLUTION I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-9195F45EDFFA</t>
         </is>
       </c>
@@ -5405,7 +5535,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5568,6 +5698,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>RIMACTANE 300 MG CAP</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-1B94CB49A6DD</t>
         </is>
       </c>
@@ -5591,7 +5726,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5758,6 +5893,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>RIMACTANE  150 MG CAP</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-B16142084FD7</t>
         </is>
       </c>
@@ -5781,7 +5921,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5954,6 +6094,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>RIFADIN CAP 300 MG</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-60F3EE2B601C</t>
         </is>
       </c>
@@ -5977,7 +6122,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6150,6 +6295,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>RIFADIN CAP 150 MG</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-2B84D0A89E12</t>
         </is>
       </c>
@@ -6173,7 +6323,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6336,6 +6486,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-BE7281B50061</t>
         </is>
       </c>
@@ -6359,7 +6514,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6514,6 +6669,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-E9E66F3ADB3B</t>
         </is>
       </c>
@@ -6537,7 +6697,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6706,6 +6866,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>RISPERDAL 1MG-ML SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-4341683EE3DA</t>
         </is>
       </c>
@@ -6729,7 +6894,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6888,6 +7053,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>RISPERDAL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-A869C28CC84D</t>
         </is>
       </c>
@@ -6911,7 +7081,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7070,6 +7240,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>RISIDONE 1MG/1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-C606470F1E9B</t>
         </is>
       </c>
@@ -7093,7 +7268,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7264,6 +7439,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Rinofed Cold &amp; Allergy Tablets</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-A1D0801495DC</t>
         </is>
       </c>
@@ -7287,7 +7467,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7454,6 +7634,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>RINOFED</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-DAEF0D85EA55</t>
         </is>
       </c>
@@ -7477,7 +7662,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7648,6 +7833,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>RINOFED PLUS TAB</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-5EB5DAC2628F</t>
         </is>
       </c>
@@ -7671,7 +7861,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7842,6 +8032,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>RINOFED PLUS SYRUP</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-E857BF7E39E8</t>
         </is>
       </c>
@@ -7865,7 +8060,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8026,6 +8221,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>RISPERDAL 2MG TAB</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-372F33F8864A</t>
         </is>
       </c>
@@ -8049,7 +8249,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8220,6 +8420,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>RINOFED EXPECTORANT SYRUP 100 ML</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-1880FF647514</t>
         </is>
       </c>
@@ -8243,7 +8448,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8406,6 +8611,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>RINOCLENIL 100MCG-DOSE NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-712C8234295E</t>
         </is>
       </c>
@@ -8429,7 +8639,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8592,6 +8802,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-48C389900370</t>
         </is>
       </c>
@@ -8615,7 +8830,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8778,6 +8993,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-E3BF9BF66F8B</t>
         </is>
       </c>
@@ -8801,7 +9021,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8960,6 +9180,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-C146EAD3E432</t>
         </is>
       </c>
@@ -8983,7 +9208,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9146,6 +9371,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E56B92D999BA</t>
         </is>
       </c>
@@ -9169,7 +9399,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9340,6 +9570,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>RIFACIN 300 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-03EC7CEC7A1E</t>
         </is>
       </c>
@@ -9363,7 +9598,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9530,6 +9765,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ROMIN 15 MG-5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-B8B6A97AEC6F</t>
         </is>
       </c>
@@ -9553,7 +9793,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9720,6 +9960,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>SAPOFEN JUNIOR 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-2DDAE06B3F0F</t>
         </is>
       </c>
@@ -9743,7 +9988,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9910,6 +10155,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>SAPOFEN JUNIOR 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-DA29FB4C4FA6</t>
         </is>
       </c>
@@ -9933,7 +10183,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10088,6 +10338,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>SAPOFEN COLD &amp; FLU TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-3D355822168B</t>
         </is>
       </c>
@@ -10111,7 +10366,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10270,6 +10525,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>SAPOFEN 600 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-1778640F4FF8</t>
         </is>
       </c>
@@ -10293,7 +10553,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10460,6 +10720,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>SAPOFEN 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-135B9FE6934C</t>
         </is>
       </c>
@@ -10483,7 +10748,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10642,6 +10907,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>SANSILLA GARGLE</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-75BC5907B1FD</t>
         </is>
       </c>
@@ -10665,7 +10935,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10832,6 +11102,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>SANCUSO 34.3 mg transdermal patch</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-BB9341C8E1E5</t>
         </is>
       </c>
@@ -10855,7 +11130,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11034,6 +11309,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>SARTAN 100 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-14C68AA4083E</t>
         </is>
       </c>
@@ -11057,7 +11337,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11232,6 +11512,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>SARTAN 50 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-73E8E3577E70</t>
         </is>
       </c>
@@ -11255,7 +11540,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11430,6 +11715,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>SELEKTINE</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-925A8E5D7C9D</t>
         </is>
       </c>
@@ -11453,7 +11743,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11624,6 +11914,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>SELECTA PLUS 5MG-12.5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-823DFCF1448C</t>
         </is>
       </c>
@@ -11647,7 +11942,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11818,6 +12113,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>SELECTA 5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-9D9D765D78BB</t>
         </is>
       </c>
@@ -11841,7 +12141,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12008,6 +12308,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>SELECTA 2.5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-EEC50DEBB6F5</t>
         </is>
       </c>
@@ -12031,7 +12336,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12198,6 +12503,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>SELECTA 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-13609F0B81C5</t>
         </is>
       </c>
@@ -12221,7 +12531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12396,6 +12706,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>SEDACORON 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-C38425A4477E</t>
         </is>
       </c>
@@ -12419,7 +12734,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12586,6 +12901,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>SECNID 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-751EE6EF9D4A</t>
         </is>
       </c>
@@ -12609,7 +12929,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12772,6 +13092,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>SECNEZOLE 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-9742F42B3CFA</t>
         </is>
       </c>
@@ -12795,7 +13120,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12962,6 +13287,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>SCANDICAINE 3% CARTRIDGE 1.8ML</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-8B8F560C4696</t>
         </is>
       </c>
@@ -12985,7 +13315,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13152,6 +13482,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>SCANDICAINE 2% SPECIALE CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-239D21A187DE</t>
         </is>
       </c>
@@ -13175,7 +13510,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13334,6 +13669,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>SAXID 4MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-3CCF90B95D22</t>
         </is>
       </c>
@@ -13357,7 +13697,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13516,6 +13856,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>SAXID 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-8E402AB5F505</t>
         </is>
       </c>
@@ -13539,7 +13884,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13702,6 +14047,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>SEDACID 20 MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-E88AE7B36897</t>
         </is>
       </c>
@@ -13725,7 +14075,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13896,6 +14246,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>SALOFALK 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-8C99DE5C2196</t>
         </is>
       </c>
@@ -13919,7 +14274,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14090,6 +14445,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>ROXONIN 60MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-B54F47643CDD</t>
         </is>
       </c>
@@ -14113,7 +14473,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14280,6 +14640,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ROXIL 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-697739C4322F</t>
         </is>
       </c>
@@ -14303,7 +14668,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14470,6 +14835,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ROXIL 250MG-5ML SUSP.</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-A8EFDC049681</t>
         </is>
       </c>
@@ -14493,7 +14863,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14652,6 +15022,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>ROTATEQ ORAL VACCINE</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-16865AA2E939</t>
         </is>
       </c>
@@ -14675,7 +15050,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14852,6 +15227,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ROTARIX ORAL SUSPENSION VACCINE</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-D1534E4A5AD2</t>
         </is>
       </c>
@@ -14875,7 +15255,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15050,6 +15430,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>ROZEX GEL 0.75% W-W</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-073B7B24054B</t>
         </is>
       </c>
@@ -15073,7 +15458,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15240,6 +15625,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>RUMAFEN</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-FB62A3054994</t>
         </is>
       </c>
@@ -15263,7 +15653,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15430,6 +15820,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>SALOFALK 4GM-60ML ENEMA</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-DF9C0B1B047D</t>
         </is>
       </c>
@@ -15453,7 +15848,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15624,6 +16019,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>SALIPAX 20</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-0B5415315C21</t>
         </is>
       </c>
@@ -15647,7 +16047,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15806,6 +16206,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>SALIDEX TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-75220817A4EE</t>
         </is>
       </c>
@@ -15829,7 +16234,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15988,6 +16393,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>SALIDEX OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-F2BAB5807998</t>
         </is>
       </c>
@@ -16011,7 +16421,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16182,6 +16592,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>SALIBET OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-43A34BFC77B0</t>
         </is>
       </c>
@@ -16205,7 +16620,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16368,6 +16783,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>RYTHINATE SUSP. 200MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-FFC85F2EE12A</t>
         </is>
       </c>
@@ -16391,7 +16811,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16554,6 +16974,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>RUMAFEN</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-139F32AE386D</t>
         </is>
       </c>
@@ -16577,7 +17002,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16752,6 +17177,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>SALBULASE 2MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-E430BA297B8B</t>
         </is>
       </c>
@@ -16775,7 +17205,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16942,6 +17372,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>SELEKTINE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-C6CD03F3EDEB</t>
         </is>
       </c>
@@ -16965,7 +17400,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17136,6 +17571,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>RIFACIN 150MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-ACF154931949</t>
         </is>
       </c>
@@ -17159,7 +17599,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17326,6 +17766,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>RIDON 4 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-2AA7B1114AAC</t>
         </is>
       </c>
@@ -17349,7 +17794,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17516,6 +17961,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-30B0D21A210E</t>
         </is>
       </c>
@@ -17539,7 +17989,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17702,6 +18152,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>RENITEC</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-9D70D17BAF96</t>
         </is>
       </c>
@@ -17725,7 +18180,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17888,6 +18343,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>RENITEC</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-DE399D4D037F</t>
         </is>
       </c>
@@ -17911,7 +18371,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18078,6 +18538,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>RENITEC</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-865F58F1D8DB</t>
         </is>
       </c>
@@ -18101,7 +18566,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18264,6 +18729,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>REMOX 500 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FB2A985ECE0A</t>
         </is>
       </c>
@@ -18287,7 +18757,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18458,6 +18928,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>REMOX 250MG -5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-86E09921BC56</t>
         </is>
       </c>
@@ -18481,7 +18956,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18648,6 +19123,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>REMOX 250 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-AC7CAC5C5931</t>
         </is>
       </c>
@@ -18671,7 +19151,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18834,6 +19314,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>REMOX 125MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-C34FB1C21DD8</t>
         </is>
       </c>
@@ -18857,7 +19342,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19020,6 +19505,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-214F6BAE85DC</t>
         </is>
       </c>
@@ -19043,7 +19533,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19218,6 +19708,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>REPARIL 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-AAC2EA27F044</t>
         </is>
       </c>
@@ -19241,7 +19736,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19408,6 +19903,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-B9D09B6ED9F4</t>
         </is>
       </c>
@@ -19431,7 +19931,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19597,6 +20097,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-226086383E7C</t>
         </is>
@@ -19613,7 +20118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19659,100 +20164,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19784,7 +20294,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19799,92 +20309,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-54077</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>447.31</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19916,7 +20431,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19931,92 +20446,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-40821</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>484.09</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20048,7 +20568,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20063,92 +20583,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-39621</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>281.17</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20180,7 +20705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20195,92 +20720,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-74296</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>483.06</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20312,7 +20842,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20327,92 +20857,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-94979</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>78.95</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20444,7 +20979,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20459,92 +20994,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-60798</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>396.4</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20576,7 +21116,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20591,92 +21131,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-85860</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>393.36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20708,7 +21253,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20723,92 +21268,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-18229</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>300.87</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20840,7 +21390,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20855,92 +21405,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-80443</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>347.26</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20972,7 +21527,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20987,92 +21542,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-83055</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>382.7</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21104,7 +21664,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21119,92 +21679,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-86649</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>428.77</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>11</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21236,7 +21801,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21251,92 +21816,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-19970</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>474.14</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>12</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21353,7 +21923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21459,6 +22029,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21494,7 +22074,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21559,6 +22139,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A3D52335B8B9</t>
         </is>
@@ -21595,7 +22185,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21660,6 +22250,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-67CDFAB83CEF</t>
         </is>
@@ -21696,7 +22296,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21761,6 +22361,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-86B28CC18212</t>
         </is>
@@ -21797,7 +22407,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21862,6 +22472,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-4214A0FA46C9</t>
         </is>
@@ -21898,7 +22518,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21963,6 +22583,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A5E5D86338DC</t>
         </is>
@@ -21999,7 +22629,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22064,6 +22694,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-CF3BA7FF392A</t>
         </is>
@@ -22100,7 +22740,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22165,6 +22805,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-FCEF2F3546DB</t>
         </is>
@@ -22201,7 +22851,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22266,6 +22916,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-FC41E2BD6B4B</t>
         </is>
@@ -22302,7 +22962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22367,6 +23027,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-5701C53DAF79</t>
         </is>
@@ -22403,7 +23073,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22468,6 +23138,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-1E62D15D8624</t>
         </is>
@@ -22504,7 +23184,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22569,6 +23249,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-E635B39187EE</t>
         </is>
@@ -22605,7 +23295,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22670,6 +23360,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-C5D1B2310947</t>
         </is>
@@ -22706,7 +23406,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22771,6 +23471,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CFD46C382355</t>
         </is>
@@ -22807,7 +23517,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22872,6 +23582,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-5955EAE18F80</t>
         </is>
@@ -22908,7 +23628,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22973,6 +23693,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-4E22F9F3269F</t>
         </is>
@@ -23009,7 +23739,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23074,6 +23804,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-07A2DDA18D84</t>
         </is>
@@ -23110,7 +23850,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23175,6 +23915,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-C89EDAE657E5</t>
         </is>
@@ -23211,7 +23961,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23276,6 +24026,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-9BF73806F915</t>
         </is>
@@ -23312,7 +24072,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23377,6 +24137,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A85D02F67892</t>
         </is>
@@ -23413,7 +24183,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23478,6 +24248,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-F98F265E9A6D</t>
         </is>

--- a/product_upload/packages/10/file.xlsx
+++ b/product_upload/packages/10/file.xlsx
@@ -1084,8 +1084,16 @@
           <t>6164034851-145-492213171976</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XANAX 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>XANAX 1 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -2067,8 +2075,16 @@
           <t>7865810267-230-187799395811</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIVOTRIL TAB 2 MG</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RIVOTRIL TAB 2 MG detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2859,8 +2875,16 @@
           <t>3864745957-718-920620555014</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISPERDAL 4MG TAB</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RISPERDAL 4MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -3048,8 +3072,16 @@
           <t>3563257332-993-855667034970</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROBITUSSIN-PE SYRUP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ROBITUSSIN-PE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3625,8 +3657,16 @@
           <t>4991499352-808-631317773731</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROFENAC GEL 1%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ROFENAC GEL 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4007,8 +4047,16 @@
           <t>2037918799-335-295950685973</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISPERDAL 3MG TAB</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RISPERDAL 3MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -4586,8 +4634,16 @@
           <t>6002858565-318-639135647149</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROFENAC 100 MG SUPP</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ROFENAC 100 MG SUPP detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4968,8 +5024,16 @@
           <t>7316023852-101-829367956420</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISPERDAL 2MG TAB</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RISPERDAL 2MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -5161,8 +5225,16 @@
           <t>2003319794-712-146043746999</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS INJECATION 500 ML SOLUTION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RINGERS INJECATION 500 ML SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5356,8 +5428,16 @@
           <t>0625919728-222-575006165263</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGER SOLUTION I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RINGER SOLUTION I.V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5543,8 +5623,16 @@
           <t>3657242743-800-004851223244</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIMACTANE 300 MG CAP</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RIMACTANE 300 MG CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5734,8 +5822,16 @@
           <t>5229329175-699-447242275477</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIMACTANE  150 MG CAP</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RIMACTANE  150 MG CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6331,8 +6427,16 @@
           <t>6307509502-061-192959502102</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6522,8 +6626,16 @@
           <t>0183508436-471-473635255993</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6902,8 +7014,16 @@
           <t>0529653529-071-439539676499</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISPERDAL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RISPERDAL 1MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7089,8 +7209,16 @@
           <t>9827710049-086-223082352714</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISIDONE 1MG/1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RISIDONE 1MG/1ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -8068,8 +8196,16 @@
           <t>5098771680-994-700602742789</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISPERDAL 2MG TAB</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RISPERDAL 2MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -8647,8 +8783,16 @@
           <t>3590509595-659-851932339520</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8838,8 +8982,16 @@
           <t>5579557505-697-823838176510</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9029,8 +9181,16 @@
           <t>8412433803-850-111465490765</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9216,8 +9376,16 @@
           <t>9693560533-200-022670724902</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RINGERS SOLUTION</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>RINGERS SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -10191,8 +10359,16 @@
           <t>5702427592-310-931003605894</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SAPOFEN COLD &amp; FLU TABLET</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SAPOFEN COLD &amp; FLU TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10374,8 +10550,16 @@
           <t>2471878945-560-804387619023</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SAPOFEN 600 MG TAB</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SAPOFEN 600 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10756,8 +10940,16 @@
           <t>9521578034-645-024314653778</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SANSILLA GARGLE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SANSILLA GARGLE detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -12937,8 +13129,16 @@
           <t>3219289482-785-512587486686</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SECNEZOLE 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SECNEZOLE 500MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13128,8 +13328,16 @@
           <t>1098728399-620-012615066015</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCANDICAINE 3% CARTRIDGE 1.8ML</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SCANDICAINE 3% CARTRIDGE 1.8ML detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13323,8 +13531,16 @@
           <t>6933810200-703-208412605618</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCANDICAINE 2% SPECIALE CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SCANDICAINE 2% SPECIALE CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13518,8 +13734,16 @@
           <t>7565982440-742-256949327903</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SAXID 4MG TABLET</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SAXID 4MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13705,8 +13929,16 @@
           <t>3778794845-805-950621848861</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SAXID 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SAXID 2MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13892,8 +14124,16 @@
           <t>0760281931-479-678220670345</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEDACID 20 MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SEDACID 20 MG COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14871,8 +15111,16 @@
           <t>1289827161-347-821471681476</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROTATEQ ORAL VACCINE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ROTATEQ ORAL VACCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -16055,8 +16303,16 @@
           <t>3743494488-359-983672098955</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALIDEX TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SALIDEX TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16242,8 +16498,16 @@
           <t>1717311934-424-530065081882</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALIDEX OINTMENT</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SALIDEX OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16628,8 +16892,16 @@
           <t>3972328428-763-795870322989</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RYTHINATE SUSP. 200MG-5ML</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>RYTHINATE SUSP. 200MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16819,8 +17091,16 @@
           <t>2035093348-633-412298775738</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RUMAFEN</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>RUMAFEN detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17213,8 +17493,16 @@
           <t>1807980091-203-350039568573</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SELEKTINE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SELEKTINE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -19350,8 +19638,16 @@
           <t>1304129472-839-070794358935</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>REPADERM GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/10/file.xlsx
+++ b/product_upload/packages/10/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22219,7 +22219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22300,40 +22300,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22413,38 +22418,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>188.13</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A3D52335B8B9</t>
         </is>
@@ -22524,38 +22534,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>139.13</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-67CDFAB83CEF</t>
         </is>
@@ -22635,38 +22650,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>164.74</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-86B28CC18212</t>
         </is>
@@ -22746,38 +22766,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>231.5</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-4214A0FA46C9</t>
         </is>
@@ -22857,38 +22882,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>306.1</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A5E5D86338DC</t>
         </is>
@@ -22968,38 +22998,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>364.86</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-CF3BA7FF392A</t>
         </is>
@@ -23079,38 +23114,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>435.21</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-FCEF2F3546DB</t>
         </is>
@@ -23190,38 +23230,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>284.8</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-FC41E2BD6B4B</t>
         </is>
@@ -23301,38 +23346,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>460.94</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-5701C53DAF79</t>
         </is>
@@ -23412,38 +23462,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>241.14</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-1E62D15D8624</t>
         </is>
@@ -23523,38 +23578,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>181.06</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-E635B39187EE</t>
         </is>
@@ -23634,38 +23694,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>423.31</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-C5D1B2310947</t>
         </is>
@@ -23745,38 +23810,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>170.15</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CFD46C382355</t>
         </is>
@@ -23856,38 +23926,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>195.42</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-5955EAE18F80</t>
         </is>
@@ -23967,38 +24042,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>404.86</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-4E22F9F3269F</t>
         </is>
@@ -24078,38 +24158,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>427.11</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-07A2DDA18D84</t>
         </is>
@@ -24189,38 +24274,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>267.35</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-C89EDAE657E5</t>
         </is>
@@ -24300,38 +24390,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>453.32</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-9BF73806F915</t>
         </is>
@@ -24411,38 +24506,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>26.08</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A85D02F67892</t>
         </is>
@@ -24522,38 +24622,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>339.69</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-F98F265E9A6D</t>
         </is>
